--- a/data/trending_integrated_20260918_11.xlsx
+++ b/data/trending_integrated_20260918_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25750</v>
+        <v>8350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.21%</t>
+          <t>'+18.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="H2" t="n">
-        <v>2.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21600</v>
+        <v>7020</v>
       </c>
       <c r="K2" t="n">
-        <v>22250</v>
+        <v>7180</v>
       </c>
       <c r="L2" t="n">
-        <v>25950</v>
+        <v>8890</v>
       </c>
       <c r="M2" t="n">
-        <v>21700</v>
+        <v>7150</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>216719051775</v>
+        <v>131615600100</v>
       </c>
       <c r="P2" t="n">
-        <v>59600</v>
+        <v>16200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1030</v>
+        <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>-170000</v>
+        <v>619000</v>
       </c>
       <c r="S2" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매수세 유입과 함께 박스권 상단 돌파 시도. 통신주 테마 흐름 속에서 25,000원 목표 가격 제시. 과거 4~5만원대 경험 언급.</t>
+          <t>상한가 안착 및 연말 목표가 언급에도 불구하고, 주가 하락 및 사기 주식에 대한 부정적 인식 확산.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['박스권', '통신주', '외인매수']</t>
+          <t>['사기주식', '주가하락', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8320</v>
+        <v>25200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.52%</t>
+          <t>'+16.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,60 +687,60 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7020</v>
+        <v>21600</v>
       </c>
       <c r="K3" t="n">
-        <v>7180</v>
+        <v>22250</v>
       </c>
       <c r="L3" t="n">
-        <v>8890</v>
+        <v>25950</v>
       </c>
       <c r="M3" t="n">
-        <v>7150</v>
+        <v>21700</v>
       </c>
       <c r="N3" t="n">
-        <v>0.59</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>130385271875</v>
+        <v>225069924400</v>
       </c>
       <c r="P3" t="n">
-        <v>16200</v>
+        <v>59600</v>
       </c>
       <c r="Q3" t="n">
-        <v>1206</v>
+        <v>1030</v>
       </c>
       <c r="R3" t="n">
-        <v>619000</v>
+        <v>-170000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>상한가 안착 및 연말 목표가 언급에도 불구하고, 주가 하락 및 사기 주식에 대한 부정적 인식 확산.</t>
+          <t>외인 및 프로그램 매수세 유입과 함께 박스권 상단 돌파 시도. 통신주 테마 흐름 속에서 25,000원 목표 가격 제시. 과거 4~5만원대 경험 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['사기주식', '주가하락', '목표가']</t>
+          <t>['박스권', '통신주', '외인매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18390</v>
+        <v>18240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.01%</t>
+          <t>'+13.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F4" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G4" t="n">
-        <v>1342</v>
+        <v>1398</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>517109474515</v>
+        <v>534373984455</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인·기관·투신 매수세 유입에 힘입어 18,000원 돌파 및 2차 매물대 공략 기대. 공매도 감소 및 숏커버링 발생 가능성 언급.</t>
+          <t>높은 수익률 달성 및 18,000원 돌파, 20,000원 목표. 외인, 기관, 투신 매수세 유입 및 공매도 청산 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['매수세', '공매도', '숏커버링']</t>
+          <t>['수익률', '외인 기관 매수', '공매도 청산']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11840</v>
+        <v>12830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.59%</t>
+          <t>'+10.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1</v>
+        <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>109</v>
+        <v>425</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10610</v>
+        <v>11580</v>
       </c>
       <c r="K5" t="n">
-        <v>10730</v>
+        <v>12200</v>
       </c>
       <c r="L5" t="n">
-        <v>12390</v>
+        <v>13820</v>
       </c>
       <c r="M5" t="n">
-        <v>10510</v>
+        <v>12100</v>
       </c>
       <c r="N5" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>84684770695</v>
+        <v>110303213700</v>
       </c>
       <c r="P5" t="n">
-        <v>14350</v>
+        <v>21150</v>
       </c>
       <c r="Q5" t="n">
-        <v>465</v>
+        <v>8140</v>
       </c>
       <c r="R5" t="n">
-        <v>30000</v>
+        <v>483000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>셀그램 관련 뉴스 기대감 속 주가 하락 및 잦은 변동성. 외인 매도세 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['셀그램', '뉴스', '외인 매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,95 +919,95 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12900</v>
+        <v>6500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.40%</t>
+          <t>'+10.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>420</v>
+        <v>113</v>
       </c>
       <c r="H6" t="n">
-        <v>8.029999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11580</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>12200</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>13820</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>12100</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>8.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>108971163270</v>
+        <v>79995242850</v>
       </c>
       <c r="P6" t="n">
-        <v>21150</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>8140</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>483000</v>
+        <v>691000</v>
       </c>
       <c r="S6" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인 투자자들의 손실 언급 및 단기 매매에 대한 부정적 전망. 일부 호재 기대에도 불구하고 주가 하락 우려.</t>
+          <t>저평가 인식과 변압기 관련주 상승 속 매수세 유입. 전환사채 발행 및 박스권 돌파 시도 관찰. 일부 매도세 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['셀그램', '단기매매', '손실']</t>
+          <t>['저평가', '변압기', '전환사채']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6510</v>
+        <v>31200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.71%</t>
+          <t>'+10.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
         <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>11.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5880</v>
+        <v>28300</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>28850</v>
       </c>
       <c r="L7" t="n">
-        <v>6920</v>
+        <v>32050</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>28550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>78440196430</v>
+        <v>148507629825</v>
       </c>
       <c r="P7" t="n">
-        <v>11760</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1620</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>691000</v>
+        <v>253000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>변압기 섹터 관련 주가 상승 기대 및 전환사채 발행 후 주가 급등 전망. 외국인 및 프매수세 유입 확인.</t>
+          <t>가온전선과의 비교 속 주가 상승 기대감. 36,000원 돌파 시도 및 매수세 유입 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['변압기', '전환사채', '외국인']</t>
+          <t>['가온전선', '주가 상승', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31100</v>
+        <v>11690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.89%</t>
+          <t>'+10.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="H8" t="n">
-        <v>11.44</v>
+        <v>12.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28300</v>
+        <v>10610</v>
       </c>
       <c r="K8" t="n">
-        <v>28850</v>
+        <v>10730</v>
       </c>
       <c r="L8" t="n">
-        <v>32050</v>
+        <v>12390</v>
       </c>
       <c r="M8" t="n">
-        <v>28550</v>
+        <v>10510</v>
       </c>
       <c r="N8" t="n">
-        <v>11.46</v>
+        <v>12.6</v>
       </c>
       <c r="O8" t="n">
-        <v>145105220400</v>
+        <v>88374707615</v>
       </c>
       <c r="P8" t="n">
-        <v>75900</v>
+        <v>14350</v>
       </c>
       <c r="Q8" t="n">
-        <v>15000</v>
+        <v>465</v>
       </c>
       <c r="R8" t="n">
-        <v>253000</v>
+        <v>30000</v>
       </c>
       <c r="S8" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 언급 및 대한전선 주가 상승 기대. 거래량 및 수급 동향에 대한 긍정적 관찰.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가온전선', '상승구간', '수급']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13900</v>
+        <v>13930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.09%</t>
+          <t>'+8.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H9" t="n">
         <v>2.83</v>
@@ -1254,7 +1254,7 @@
         <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>120722068355</v>
+        <v>122048286360</v>
       </c>
       <c r="P9" t="n">
         <v>20300</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1823000</v>
+        <v>1820000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>466</v>
       </c>
       <c r="G10" t="n">
-        <v>3081</v>
+        <v>2903</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1915580699000</v>
+        <v>1985476996000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 반도체 관련 긍정적 뉴스 및 미국 증시 상승에 따른 SK하이닉스 주가 급등 기대. 공급 부족 장기화 전망.</t>
+          <t>미국 증시 및 반도체 지수 강세에 따른 주가 상승 기대. 연말 500, 200 돌파 목표 제시. 공급 부족 전망 및 외인 매수세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI반도체', '공급부족', '미국증시']</t>
+          <t>['반도체', '공급 부족', '외인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19270</v>
+        <v>13860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.22%</t>
+          <t>'+3.98%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>4.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18490</v>
+        <v>13330</v>
       </c>
       <c r="K11" t="n">
-        <v>18900</v>
+        <v>13600</v>
       </c>
       <c r="L11" t="n">
-        <v>19700</v>
+        <v>13930</v>
       </c>
       <c r="M11" t="n">
-        <v>18770</v>
+        <v>13210</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85</v>
+        <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>89954436850</v>
+        <v>40915111730</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>392000</v>
+        <v>68000</v>
       </c>
       <c r="S11" t="n">
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 주가 방어 언급 및 중동 전쟁 관련 이슈에 대한 기대감. 주가 상승에 대한 긍정적 전망.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '주가상승', '중동전쟁']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13870</v>
+        <v>19200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.82%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>182</v>
+        <v>306</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10.74</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,130 +1515,130 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13360</v>
+        <v>18490</v>
       </c>
       <c r="K12" t="n">
-        <v>13450</v>
+        <v>18900</v>
       </c>
       <c r="L12" t="n">
-        <v>14450</v>
+        <v>19700</v>
       </c>
       <c r="M12" t="n">
-        <v>13450</v>
+        <v>18770</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>29549734290</v>
+        <v>91143958200</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>392000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>미국 원전주 상승 및 중동 전쟁 종전 논의 속 주가 상승 기대. 대차해지 운동과 공사 수주 계약 (신대방역세권) 사실 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>['대차해지', '공사 수주', '원전주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13830</v>
+        <v>53000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.75%</t>
+          <t>'+3.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>321</v>
       </c>
       <c r="H13" t="n">
-        <v>4.92</v>
+        <v>38.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13330</v>
+        <v>51100</v>
       </c>
       <c r="K13" t="n">
-        <v>13600</v>
+        <v>51600</v>
       </c>
       <c r="L13" t="n">
-        <v>13930</v>
+        <v>55200</v>
       </c>
       <c r="M13" t="n">
-        <v>13210</v>
+        <v>51500</v>
       </c>
       <c r="N13" t="n">
-        <v>4.99</v>
+        <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>39958942785</v>
+        <v>170610130150</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>68000</v>
+        <v>499000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>123000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53000</v>
+        <v>18440</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>310</v>
+        <v>222</v>
       </c>
       <c r="H14" t="n">
-        <v>38.54</v>
+        <v>0.98</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51100</v>
+        <v>17930</v>
       </c>
       <c r="K14" t="n">
-        <v>51600</v>
+        <v>18400</v>
       </c>
       <c r="L14" t="n">
-        <v>55200</v>
+        <v>20400</v>
       </c>
       <c r="M14" t="n">
-        <v>51500</v>
+        <v>17910</v>
       </c>
       <c r="N14" t="n">
-        <v>38.62</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>167675155050</v>
+        <v>66503189475</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>21100</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>9900</v>
       </c>
       <c r="R14" t="n">
-        <v>499000</v>
+        <v>32000</v>
       </c>
       <c r="S14" t="n">
-        <v>123000</v>
+        <v>22000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
+          <t>기술이전 및 3상 임상 관련 뉴스 기대감 속 기관, 외인 매수세 관찰. 락업 해제 물량 및 프로그램 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
+          <t>['기술이전', '3상 임상', '기관 외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,174 +1747,174 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18480</v>
+        <v>13710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H15" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17930</v>
+        <v>13360</v>
       </c>
       <c r="K15" t="n">
-        <v>18400</v>
+        <v>13450</v>
       </c>
       <c r="L15" t="n">
-        <v>20400</v>
+        <v>14450</v>
       </c>
       <c r="M15" t="n">
-        <v>17910</v>
+        <v>13450</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>65402469220</v>
+        <v>30573676285</v>
       </c>
       <c r="P15" t="n">
-        <v>21100</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>9900</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기관 및 외인 매수세 확인과 함께 기술이전 및 3상 진행에 대한 긍정적 전망. 목표가 5만원 언급.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기술이전', '3상', '기관외인']</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>259000</v>
+        <v>17680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>1681</v>
+        <v>129</v>
       </c>
       <c r="H16" t="n">
-        <v>46.48</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>252500</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>261000</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>261000</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>257500</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
-        <v>46.52</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1093047069500</v>
+        <v>67734948850</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>78600</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>-601000</v>
+        <v>-137000</v>
       </c>
       <c r="S16" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 타 종목과의 주가 비교 언급. 특정 시점 이전 주가 상승에 대한 부정적 전망.</t>
+          <t>미증시 양자컴퓨터 주식 급등에 따른 관련주 동반 상승 기대감. 단기 과열 우려 및 개인 투자자 포지션에 대한 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,90 +1923,90 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['이재명', '저평가', '주가 상승']</t>
+          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17600</v>
+        <v>258750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>474</v>
       </c>
       <c r="G17" t="n">
-        <v>126</v>
+        <v>1710</v>
       </c>
       <c r="H17" t="n">
-        <v>0.97</v>
+        <v>46.48</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17250</v>
+        <v>252500</v>
       </c>
       <c r="K17" t="n">
-        <v>17920</v>
+        <v>261000</v>
       </c>
       <c r="L17" t="n">
-        <v>18440</v>
+        <v>261000</v>
       </c>
       <c r="M17" t="n">
-        <v>17450</v>
+        <v>257500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>46.52</v>
       </c>
       <c r="O17" t="n">
-        <v>67072788650</v>
+        <v>1127485551750</v>
       </c>
       <c r="P17" t="n">
-        <v>30550</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>6100</v>
+        <v>78600</v>
       </c>
       <c r="R17" t="n">
-        <v>-137000</v>
+        <v>-601000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미증시 양자컴퓨터 주식 급등에 따른 관련주 동반 상승 기대감. 단기 과열 우려 및 개인 투자자 포지션에 대한 언급.</t>
+          <t>정치적 언급 다수. 주가 상승 및 하락에 대한 다양한 전망 혼재. 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,20 +2015,20 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
+          <t>['주가 전망', '정치', '개미']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F18" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G18" t="n">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>72997997350</v>
+        <v>74357164050</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10210</v>
+        <v>10190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>20098356275</v>
+        <v>20369985120</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4210</v>
+        <v>4215</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-9.06%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F20" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G20" t="n">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>29661628567</v>
+        <v>30129580994</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_11.xlsx
+++ b/data/trending_integrated_20260918_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8350</v>
+        <v>8320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.95%</t>
+          <t>'+18.52%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>131615600100</v>
+        <v>132334472500</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>상한가 안착 및 연말 목표가 언급에도 불구하고, 주가 하락 및 사기 주식에 대한 부정적 인식 확산.</t>
+          <t>상한가 및 10000원 돌파에 대한 기대감과 함께, 외국인 및 기관의 매수세를 긍정적으로 해석하는 의견이 존재함. 다만, 높은 매물대와 급락 가능성에 대한 우려도 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사기주식', '주가하락', '목표가']</t>
+          <t>['상한가', '외국인', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25200</v>
+        <v>25400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.67%</t>
+          <t>'+17.59%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H3" t="n">
         <v>2.41</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>225069924400</v>
+        <v>232462851100</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18240</v>
+        <v>18270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.08%</t>
+          <t>'+13.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="F4" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
-        <v>1398</v>
+        <v>1430</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>534373984455</v>
+        <v>541342392625</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12830</v>
+        <v>31450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.79%</t>
+          <t>'+11.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.67</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>425</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
-        <v>8.029999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11580</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>12200</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>13820</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>12100</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>8.699999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>110303213700</v>
+        <v>153208217150</v>
       </c>
       <c r="P5" t="n">
-        <v>21150</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>8140</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>483000</v>
+        <v>253000</v>
       </c>
       <c r="S5" t="n">
-        <v>107000</v>
+        <v>29000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감 속 주가 하락 및 잦은 변동성. 외인 매도세 확인.</t>
+          <t>가온전선과의 비교 언급이 많으며, 주가 상승에 대한 기대와 지루함이 혼재되어 있음. 단기적인 주가 움직임에 대한 관망세가 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['셀그램', '뉴스', '외인 매도']</t>
+          <t>['가온전선', '저평가', '단타']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6500</v>
+        <v>12860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.54%</t>
+          <t>'+11.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>113</v>
+        <v>441</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5880</v>
+        <v>11580</v>
       </c>
       <c r="K6" t="n">
-        <v>5950</v>
+        <v>12200</v>
       </c>
       <c r="L6" t="n">
-        <v>6920</v>
+        <v>13820</v>
       </c>
       <c r="M6" t="n">
-        <v>5840</v>
+        <v>12100</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>79995242850</v>
+        <v>110933217800</v>
       </c>
       <c r="P6" t="n">
-        <v>11760</v>
+        <v>21150</v>
       </c>
       <c r="Q6" t="n">
-        <v>1620</v>
+        <v>8140</v>
       </c>
       <c r="R6" t="n">
-        <v>691000</v>
+        <v>483000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저평가 인식과 변압기 관련주 상승 속 매수세 유입. 전환사채 발행 및 박스권 돌파 시도 관찰. 일부 매도세 존재.</t>
+          <t>개인 투자자들의 잦은 손실과 종목에 대한 부정적인 전망. 일부 투자자들은 '진성주주'만 남았다고 주장하나, 전반적으로 혼란스러운 심리가 감지됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '변압기', '전환사채']</t>
+          <t>['손실', '진성주주', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31200</v>
+        <v>6520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.25%</t>
+          <t>'+10.88%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="H7" t="n">
-        <v>11.44</v>
+        <v>2.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28300</v>
+        <v>5880</v>
       </c>
       <c r="K7" t="n">
-        <v>28850</v>
+        <v>5950</v>
       </c>
       <c r="L7" t="n">
-        <v>32050</v>
+        <v>6920</v>
       </c>
       <c r="M7" t="n">
-        <v>28550</v>
+        <v>5840</v>
       </c>
       <c r="N7" t="n">
-        <v>11.46</v>
+        <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>148507629825</v>
+        <v>80676326135</v>
       </c>
       <c r="P7" t="n">
-        <v>75900</v>
+        <v>11760</v>
       </c>
       <c r="Q7" t="n">
-        <v>15000</v>
+        <v>1620</v>
       </c>
       <c r="R7" t="n">
-        <v>253000</v>
+        <v>691000</v>
       </c>
       <c r="S7" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 주가 상승 기대감. 36,000원 돌파 시도 및 매수세 유입 관찰.</t>
+          <t>전환사채 발행 이후에도 주가 상승 가능성을 높게 보며, 저평가 해소 및 박스권 돌파에 대한 기대감이 강함. 외인, 프매, 기법 등 기관 수급 분석이 긍정적으로 작용.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가온전선', '주가 상승', '매수세']</t>
+          <t>['전환사채', '저평가', '기관 수급']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11690</v>
+        <v>13970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.18%</t>
+          <t>'+8.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="H8" t="n">
-        <v>12.5</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10610</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>10730</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>12390</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>10510</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>12.6</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>88374707615</v>
+        <v>123825873040</v>
       </c>
       <c r="P8" t="n">
-        <v>14350</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>465</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13930</v>
+        <v>11710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.32%</t>
+          <t>'+5.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>2.83</v>
+        <v>12.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12860</v>
+        <v>11080</v>
       </c>
       <c r="K9" t="n">
-        <v>13020</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14230</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.83</v>
+        <v>12.6</v>
       </c>
       <c r="O9" t="n">
-        <v>122048286360</v>
+        <v>89904000000</v>
       </c>
       <c r="P9" t="n">
-        <v>20300</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2885</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="S9" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1820000</v>
+        <v>1823000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G10" t="n">
-        <v>2903</v>
+        <v>2751</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1985476996000</v>
+        <v>2072458196000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체 지수 강세에 따른 주가 상승 기대. 연말 500, 200 돌파 목표 제시. 공급 부족 전망 및 외인 매수세 관찰.</t>
+          <t>반도체 업황 개선 및 미증시 상승에 따른 주가 상승 기대감이 높음. 연말 목표가 상향 조정과 함께 추석 랠리에 대한 언급도 나타남. 반도체 관련 뉴스가 긍정적으로 작용.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '공급 부족', '외인 매수']</t>
+          <t>['반도체', '미증시', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13860</v>
+        <v>13890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+4.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1429,7 +1429,7 @@
         <v>13600</v>
       </c>
       <c r="L11" t="n">
-        <v>13930</v>
+        <v>13940</v>
       </c>
       <c r="M11" t="n">
         <v>13210</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>40915111730</v>
+        <v>44141857010</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19200</v>
+        <v>19240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.84%</t>
+          <t>'+4.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,7 +1501,7 @@
         <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
         <v>306</v>
@@ -1530,7 +1530,7 @@
         <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>91143958200</v>
+        <v>92341282395</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53000</v>
+        <v>52700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="H13" t="n">
         <v>38.54</v>
@@ -1622,7 +1622,7 @@
         <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>170610130150</v>
+        <v>175449965450</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18440</v>
+        <v>259000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>472</v>
       </c>
       <c r="G14" t="n">
-        <v>222</v>
+        <v>1719</v>
       </c>
       <c r="H14" t="n">
-        <v>0.98</v>
+        <v>46.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17930</v>
+        <v>252500</v>
       </c>
       <c r="K14" t="n">
-        <v>18400</v>
+        <v>261000</v>
       </c>
       <c r="L14" t="n">
-        <v>20400</v>
+        <v>261000</v>
       </c>
       <c r="M14" t="n">
-        <v>17910</v>
+        <v>257500</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>66503189475</v>
+        <v>1210628930250</v>
       </c>
       <c r="P14" t="n">
-        <v>21100</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>9900</v>
+        <v>78600</v>
       </c>
       <c r="R14" t="n">
-        <v>32000</v>
+        <v>-601000</v>
       </c>
       <c r="S14" t="n">
-        <v>22000</v>
+        <v>333000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기술이전 및 3상 임상 관련 뉴스 기대감 속 기관, 외인 매수세 관찰. 락업 해제 물량 및 프로그램 매매 동향 주시.</t>
+          <t>정치적 발언이 주를 이루며, 주가 상승에 대한 기대보다는 정치적 상황에 대한 부정적인 논평이 주를 이룸. 주가 관련 구체적인 팩트 언급은 거의 없음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기술이전', '3상 임상', '기관 외인 매수']</t>
+          <t>['이재명', '대통령', '주가 상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13710</v>
+        <v>13700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30573676285</v>
+        <v>31185282865</v>
       </c>
       <c r="P15" t="n">
         <v>19380</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17680</v>
+        <v>17590</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.49%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H16" t="n">
         <v>0.97</v>
@@ -1898,7 +1898,7 @@
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>67734948850</v>
+        <v>68137384400</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>258750</v>
+        <v>18270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.48%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F17" t="n">
-        <v>474</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>1710</v>
+        <v>228</v>
       </c>
       <c r="H17" t="n">
-        <v>46.48</v>
+        <v>0.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>252500</v>
+        <v>17930</v>
       </c>
       <c r="K17" t="n">
-        <v>261000</v>
+        <v>18400</v>
       </c>
       <c r="L17" t="n">
-        <v>261000</v>
+        <v>20400</v>
       </c>
       <c r="M17" t="n">
-        <v>257500</v>
+        <v>17910</v>
       </c>
       <c r="N17" t="n">
-        <v>46.52</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1127485551750</v>
+        <v>68795628235</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>21100</v>
       </c>
       <c r="Q17" t="n">
-        <v>78600</v>
+        <v>9900</v>
       </c>
       <c r="R17" t="n">
-        <v>-601000</v>
+        <v>32000</v>
       </c>
       <c r="S17" t="n">
-        <v>333000</v>
+        <v>22000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치적 언급 다수. 주가 상승 및 하락에 대한 다양한 전망 혼재. 명확한 근거 제시 부족.</t>
+          <t>기술이전 및 3상 임상 관련 뉴스 기대감 속 기관, 외인 매수세 관찰. 락업 해제 물량 및 프로그램 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 전망', '정치', '개미']</t>
+          <t>['기술이전', '3상 임상', '기관 외인 매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G18" t="n">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>74357164050</v>
+        <v>75252098450</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
+          <t>미국 증시 원전주 급등 및 대미 투자 관련 발표 가능성에 대한 뉴스가 주가 상승 모멘텀으로 작용. 120일선 돌파 및 정배열 가능성에 대한 긍정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '120일선']</t>
+          <t>['원전주', '대미 투자', '정배열']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10190</v>
+        <v>10210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.95%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>20369985120</v>
+        <v>20597856055</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4215</v>
+        <v>4200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.06%</t>
+          <t>'-9.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F20" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>30129580994</v>
+        <v>30436559704</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_11.xlsx
+++ b/data/trending_integrated_20260918_11.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8320</v>
+        <v>8330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.52%</t>
+          <t>'+18.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>132334472500</v>
+        <v>134722611015</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>상한가 및 10000원 돌파에 대한 기대감과 함께, 외국인 및 기관의 매수세를 긍정적으로 해석하는 의견이 존재함. 다만, 높은 매물대와 급락 가능성에 대한 우려도 공존.</t>
+          <t>연말까지 홀딩하며 평정심 유지 강조. 일부 매물대 및 하락 우려 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상한가', '외국인', '매물대']</t>
+          <t>['홀딩', '평정심', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25400</v>
+        <v>25450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.59%</t>
+          <t>'+17.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
         <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
         <v>2.41</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>232462851100</v>
+        <v>235975578825</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18270</v>
+        <v>18300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.27%</t>
+          <t>'+13.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F4" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G4" t="n">
-        <v>1430</v>
+        <v>1477</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>541342392625</v>
+        <v>549235606250</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>높은 수익률 달성 및 18,000원 돌파, 20,000원 목표. 외인, 기관, 투신 매수세 유입 및 공매도 청산 기대.</t>
+          <t>높은 수익률 달성 및 2차 매물대 돌파, 숏커버링 발생 등 긍정적 지표 언급. 외인/기관 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수익률', '외인 기관 매수', '공매도 청산']</t>
+          <t>['수익률', '숏커버링', '매수세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,79 +839,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31450</v>
+        <v>6560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.13%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="H5" t="n">
-        <v>11.44</v>
+        <v>2.85</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>28300</v>
+        <v>5880</v>
       </c>
       <c r="K5" t="n">
-        <v>28850</v>
+        <v>5950</v>
       </c>
       <c r="L5" t="n">
-        <v>32050</v>
+        <v>6920</v>
       </c>
       <c r="M5" t="n">
-        <v>28550</v>
+        <v>5840</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>153208217150</v>
+        <v>81376781310</v>
       </c>
       <c r="P5" t="n">
-        <v>75900</v>
+        <v>11760</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000</v>
+        <v>1620</v>
       </c>
       <c r="R5" t="n">
-        <v>253000</v>
+        <v>691000</v>
       </c>
       <c r="S5" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 언급이 많으며, 주가 상승에 대한 기대와 지루함이 혼재되어 있음. 단기적인 주가 움직임에 대한 관망세가 나타남.</t>
+          <t>박스권 돌파 및 저평가 상태 언급. 전환사채 발행 가능성과 변압기 관련주 비교. 매도 의견 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가온전선', '저평가', '단타']</t>
+          <t>['박스권 돌파', '저평가', '전환사채']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12860</v>
+        <v>12910</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.05%</t>
+          <t>'+11.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
@@ -978,7 +978,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>110933217800</v>
+        <v>111560552920</v>
       </c>
       <c r="P6" t="n">
         <v>21150</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인 투자자들의 잦은 손실과 종목에 대한 부정적인 전망. 일부 투자자들은 '진성주주'만 남았다고 주장하나, 전반적으로 혼란스러운 심리가 감지됨.</t>
+          <t>감정적인 매도 의견과 일부 호재 언급. 명확한 근거 없이 주가 하락 및 회복에 대한 기대와 우려가 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['손실', '진성주주', '전망']</t>
+          <t>['셀그램', '호재', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6520</v>
+        <v>31500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.88%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>11.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5880</v>
+        <v>28300</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>28850</v>
       </c>
       <c r="L7" t="n">
-        <v>6920</v>
+        <v>32050</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>28550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>80676326135</v>
+        <v>157368948925</v>
       </c>
       <c r="P7" t="n">
-        <v>11760</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1620</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>691000</v>
+        <v>253000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전환사채 발행 이후에도 주가 상승 가능성을 높게 보며, 저평가 해소 및 박스권 돌파에 대한 기대감이 강함. 외인, 프매, 기법 등 기관 수급 분석이 긍정적으로 작용.</t>
+          <t>가온전선과의 비교 속에서 저평가 해소 기대감 및 주가 상승 언급. 일부 매도 의견 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전환사채', '저평가', '기관 수급']</t>
+          <t>['저평가', '가온전선', '주가 상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13970</v>
+        <v>11670</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.63%</t>
+          <t>'+9.99%</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>112</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>10610</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10730</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12390</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10510</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>91385325810</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>465</v>
+      </c>
+      <c r="R8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>68</v>
-      </c>
-      <c r="F8" t="n">
-        <v>38</v>
-      </c>
-      <c r="G8" t="n">
-        <v>127</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M8" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O8" t="n">
-        <v>123825873040</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>48000</v>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11710</v>
+        <v>13970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.69%</t>
+          <t>'+8.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H9" t="n">
-        <v>12.5</v>
+        <v>2.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11080</v>
+        <v>12860</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>13020</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>14230</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="N9" t="n">
-        <v>12.6</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>89904000000</v>
+        <v>125129038425</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="R9" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1823000</v>
+        <v>1822000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="G10" t="n">
-        <v>2751</v>
+        <v>2644</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2072458196000</v>
+        <v>2143219018000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 미증시 상승에 따른 주가 상승 기대감이 높음. 연말 목표가 상향 조정과 함께 추석 랠리에 대한 언급도 나타남. 반도체 관련 뉴스가 긍정적으로 작용.</t>
+          <t>연말 500 예상 및 반도체 시장의 긍정적 전망, 미증시 급등에 따른 동반 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '미증시', '목표가']</t>
+          <t>['반도체', '미증시', '동반 상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>44141857010</v>
+        <v>45284281655</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.06%</t>
+          <t>'+4.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="H12" t="n">
         <v>10.74</v>
@@ -1530,7 +1530,7 @@
         <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>92341282395</v>
+        <v>93329608675</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전주 상승 및 중동 전쟁 종전 논의 속 주가 상승 기대. 대차해지 운동과 공사 수주 계약 (신대방역세권) 사실 확인.</t>
+          <t>대차해지 운동을 통한 주가 방어 및 상승 기대감 표출. 미국장 및 중동 전쟁 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '공사 수주', '원전주']</t>
+          <t>['대차해지', '주가 방어', '미국장']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52700</v>
+        <v>52900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.13%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="H13" t="n">
         <v>38.54</v>
@@ -1622,7 +1622,7 @@
         <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>175449965450</v>
+        <v>177463040650</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>259000</v>
+        <v>259500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.77%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="G14" t="n">
-        <v>1719</v>
+        <v>1824</v>
       </c>
       <c r="H14" t="n">
         <v>46.48</v>
@@ -1714,7 +1714,7 @@
         <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>1210628930250</v>
+        <v>1241051462750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 발언이 주를 이루며, 주가 상승에 대한 기대보다는 정치적 상황에 대한 부정적인 논평이 주를 이룸. 주가 관련 구체적인 팩트 언급은 거의 없음.</t>
+          <t>정치적 이슈에 대한 부정적 언급이 주를 이루며, 주가 관련 내용은 미미함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재명', '대통령', '주가 상승']</t>
+          <t>['하야', '이재명', '기자회견']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>31185282865</v>
+        <v>31530946415</v>
       </c>
       <c r="P15" t="n">
         <v>19380</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17590</v>
+        <v>17610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
         <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H16" t="n">
         <v>0.97</v>
@@ -1898,7 +1898,7 @@
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>68137384400</v>
+        <v>68460603700</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18270</v>
+        <v>18070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+0.78%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>68795628235</v>
+        <v>70039707105</v>
       </c>
       <c r="P17" t="n">
         <v>21100</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>기술이전 및 3상 임상 관련 뉴스 기대감 속 기관, 외인 매수세 관찰. 락업 해제 물량 및 프로그램 매매 동향 주시.</t>
+          <t>머크 3상 임상 진행 및 빅파마 기술이전 가능성 언급. 락업 해제 및 프로그램 매매 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['기술이전', '3상 임상', '기관 외인 매수']</t>
+          <t>['3상', '기술이전', '락업해제']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F18" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G18" t="n">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>75252098450</v>
+        <v>76612929600</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등 및 대미 투자 관련 발표 가능성에 대한 뉴스가 주가 상승 모멘텀으로 작용. 120일선 돌파 및 정배열 가능성에 대한 긍정적 전망이 우세.</t>
+          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 언급. 120일선 돌파 기대감. 외인 매도세 속 개인 투자자 참여.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '정배열']</t>
+          <t>['원전주', '대미투자', '외인']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10210</v>
+        <v>10230</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>20597856055</v>
+        <v>20817936300</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4200</v>
+        <v>4165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.39%</t>
+          <t>'-10.14%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2260,13 +2260,13 @@
         <v>4535</v>
       </c>
       <c r="M20" t="n">
-        <v>4165</v>
+        <v>4145</v>
       </c>
       <c r="N20" t="n">
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>30436559704</v>
+        <v>31297100986</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 호재. 그러나 급락 및 공매도 우려.</t>
+          <t>STO 사업 추진 및 코인 관련 호재 언급 속 하락세 지속. 공매도 압박 및 주가 하락 예상.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['STO', '암호화폐', '공매도']</t>
+          <t>['STO', '코인', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-27.91%</t>
+          <t>'-23.26%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>
@@ -2358,7 +2358,7 @@
         <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>113129219</v>
+        <v>124592693</v>
       </c>
       <c r="P21" t="n">
         <v>901</v>

--- a/data/trending_integrated_20260918_11.xlsx
+++ b/data/trending_integrated_20260918_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8330</v>
+        <v>8370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.66%</t>
+          <t>'+19.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>134722611015</v>
+        <v>135793291690</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25450</v>
+        <v>25400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.82%</t>
+          <t>'+17.59%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>64</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>235975578825</v>
+        <v>238484105325</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매수세 유입과 함께 박스권 상단 돌파 시도. 통신주 테마 흐름 속에서 25,000원 목표 가격 제시. 과거 4~5만원대 경험 언급.</t>
+          <t>외인 폭풍 매수 확인. 박스권 상단 돌파 및 대장주 움직임 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['박스권', '통신주', '외인매수']</t>
+          <t>['외인', '매수', '박스권']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18300</v>
+        <v>18500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.45%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F4" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G4" t="n">
-        <v>1477</v>
+        <v>1556</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -785,7 +785,7 @@
         <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>18460</v>
+        <v>18500</v>
       </c>
       <c r="M4" t="n">
         <v>16170</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>549235606250</v>
+        <v>564870798060</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,12 +810,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>높은 수익률 달성 및 2차 매물대 돌파, 숏커버링 발생 등 긍정적 지표 언급. 외인/기관 매수세 확인.</t>
+          <t>수익률 500% 이상 달성 언급. 숏커버링 발생 및 외인 기관 투신 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -839,79 +839,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6560</v>
+        <v>31550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.56%</t>
+          <t>'+11.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="H5" t="n">
-        <v>2.85</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5880</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>5950</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>6920</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>5840</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>81376781310</v>
+        <v>164157481075</v>
       </c>
       <c r="P5" t="n">
-        <v>11760</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1620</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>691000</v>
+        <v>253000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 저평가 상태 언급. 전환사채 발행 가능성과 변압기 관련주 비교. 매도 의견 존재.</t>
+          <t>가온전선 대비 저평가 해소 기대. 연기금 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '저평가', '전환사채']</t>
+          <t>['저평가', '연기금', '매수세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12910</v>
+        <v>12890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.49%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
         <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
@@ -978,7 +978,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>111560552920</v>
+        <v>111990884700</v>
       </c>
       <c r="P6" t="n">
         <v>21150</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31500</v>
+        <v>11710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+10.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="H7" t="n">
-        <v>11.44</v>
+        <v>12.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,152 +1055,152 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28300</v>
+        <v>10610</v>
       </c>
       <c r="K7" t="n">
-        <v>28850</v>
+        <v>10730</v>
       </c>
       <c r="L7" t="n">
-        <v>32050</v>
+        <v>12390</v>
       </c>
       <c r="M7" t="n">
-        <v>28550</v>
+        <v>10510</v>
       </c>
       <c r="N7" t="n">
-        <v>11.46</v>
+        <v>12.6</v>
       </c>
       <c r="O7" t="n">
-        <v>157368948925</v>
+        <v>92917928560</v>
       </c>
       <c r="P7" t="n">
-        <v>75900</v>
+        <v>14350</v>
       </c>
       <c r="Q7" t="n">
-        <v>15000</v>
+        <v>465</v>
       </c>
       <c r="R7" t="n">
-        <v>253000</v>
+        <v>30000</v>
       </c>
       <c r="S7" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속에서 저평가 해소 기대감 및 주가 상승 언급. 일부 매도 의견 존재.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['저평가', '가온전선', '주가 상승']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11670</v>
+        <v>6470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.99%</t>
+          <t>'+10.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>1.02</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H8" t="n">
-        <v>12.5</v>
+        <v>2.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10610</v>
+        <v>5880</v>
       </c>
       <c r="K8" t="n">
-        <v>10730</v>
+        <v>5950</v>
       </c>
       <c r="L8" t="n">
-        <v>12390</v>
+        <v>6920</v>
       </c>
       <c r="M8" t="n">
-        <v>10510</v>
+        <v>5840</v>
       </c>
       <c r="N8" t="n">
-        <v>12.6</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>91385325810</v>
+        <v>81923254005</v>
       </c>
       <c r="P8" t="n">
-        <v>14350</v>
+        <v>11760</v>
       </c>
       <c r="Q8" t="n">
-        <v>465</v>
+        <v>1620</v>
       </c>
       <c r="R8" t="n">
-        <v>30000</v>
+        <v>691000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>박스권 돌파 및 저평가 상태 언급. 전환사채 발행 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['박스권', '저평가', '전환사채']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H9" t="n">
         <v>2.83</v>
@@ -1254,7 +1254,7 @@
         <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>125129038425</v>
+        <v>126536811975</v>
       </c>
       <c r="P9" t="n">
         <v>20300</v>
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1822000</v>
+        <v>13950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>458</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>2644</v>
+        <v>413</v>
       </c>
       <c r="H10" t="n">
-        <v>50.1</v>
+        <v>4.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1745000</v>
+        <v>13330</v>
       </c>
       <c r="K10" t="n">
-        <v>1810000</v>
+        <v>13600</v>
       </c>
       <c r="L10" t="n">
-        <v>1828000</v>
+        <v>14030</v>
       </c>
       <c r="M10" t="n">
-        <v>1805000</v>
+        <v>13210</v>
       </c>
       <c r="N10" t="n">
-        <v>50.2</v>
+        <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>2143219018000</v>
+        <v>50319726095</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>30200</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>3540</v>
       </c>
       <c r="R10" t="n">
-        <v>212000</v>
+        <v>68000</v>
       </c>
       <c r="S10" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>연말 500 예상 및 반도체 시장의 긍정적 전망, 미증시 급등에 따른 동반 상승 기대감 표출.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '미증시', '동반 상승']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13890</v>
+        <v>1823000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.20%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>460</v>
       </c>
       <c r="G11" t="n">
-        <v>353</v>
+        <v>2592</v>
       </c>
       <c r="H11" t="n">
-        <v>4.92</v>
+        <v>50.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13330</v>
+        <v>1745000</v>
       </c>
       <c r="K11" t="n">
-        <v>13600</v>
+        <v>1810000</v>
       </c>
       <c r="L11" t="n">
-        <v>13940</v>
+        <v>1828000</v>
       </c>
       <c r="M11" t="n">
-        <v>13210</v>
+        <v>1805000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.99</v>
+        <v>50.2</v>
       </c>
       <c r="O11" t="n">
-        <v>45284281655</v>
+        <v>2227295082500</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>68000</v>
+        <v>212000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>미국 증시 반도체주 급등 영향. 반도체 펀더멘털 튼튼 및 수요 많음 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['반도체', '수요', '펀더멘털']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19230</v>
+        <v>19290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.00%</t>
+          <t>'+4.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H12" t="n">
         <v>10.74</v>
@@ -1530,7 +1530,7 @@
         <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>93329608675</v>
+        <v>94378722850</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 주가 방어 및 상승 기대감 표출. 미국장 및 중동 전쟁 관련 언급.</t>
+          <t>대차해지 운동 동참 요구. 중동 전쟁 종전 논의 및 하반기 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '주가 방어', '미국장']</t>
+          <t>['대차해지', '중동 전쟁', '상승 기대']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52900</v>
+        <v>13780</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.52%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>352</v>
+        <v>232</v>
       </c>
       <c r="H13" t="n">
-        <v>38.54</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>51100</v>
+        <v>13360</v>
       </c>
       <c r="K13" t="n">
-        <v>51600</v>
+        <v>13450</v>
       </c>
       <c r="L13" t="n">
-        <v>55200</v>
+        <v>14450</v>
       </c>
       <c r="M13" t="n">
-        <v>51500</v>
+        <v>13450</v>
       </c>
       <c r="N13" t="n">
-        <v>38.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>177463040650</v>
+        <v>32099337640</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>499000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>123000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>259500</v>
+        <v>52600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.77%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>462</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>1824</v>
+        <v>358</v>
       </c>
       <c r="H14" t="n">
-        <v>46.48</v>
+        <v>38.54</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>252500</v>
+        <v>51100</v>
       </c>
       <c r="K14" t="n">
-        <v>261000</v>
+        <v>51600</v>
       </c>
       <c r="L14" t="n">
-        <v>261000</v>
+        <v>55200</v>
       </c>
       <c r="M14" t="n">
-        <v>257500</v>
+        <v>51500</v>
       </c>
       <c r="N14" t="n">
-        <v>46.52</v>
+        <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>1241051462750</v>
+        <v>180618295700</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>78600</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-601000</v>
+        <v>499000</v>
       </c>
       <c r="S14" t="n">
-        <v>333000</v>
+        <v>123000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급이 주를 이루며, 주가 관련 내용은 미미함.</t>
+          <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하야', '이재명', '기자회견']</t>
+          <t>['외인', '기관', '매수세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13700</v>
+        <v>259000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>454</v>
       </c>
       <c r="G15" t="n">
-        <v>214</v>
+        <v>1845</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>46.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13360</v>
+        <v>252500</v>
       </c>
       <c r="K15" t="n">
-        <v>13450</v>
+        <v>261000</v>
       </c>
       <c r="L15" t="n">
-        <v>14450</v>
+        <v>261000</v>
       </c>
       <c r="M15" t="n">
-        <v>13450</v>
+        <v>257500</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>46.52</v>
       </c>
       <c r="O15" t="n">
-        <v>31530946415</v>
+        <v>1276087076500</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>78600</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-601000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>정치 관련 내용 중심, 주가 상승 관련 내용은 적음.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17610</v>
+        <v>17600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H16" t="n">
         <v>0.97</v>
@@ -1898,7 +1898,7 @@
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>68460603700</v>
+        <v>68652716070</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18070</v>
+        <v>18080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.78%</t>
+          <t>'+0.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>70039707105</v>
+        <v>70756277325</v>
       </c>
       <c r="P17" t="n">
         <v>21100</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>머크 3상 임상 진행 및 빅파마 기술이전 가능성 언급. 락업 해제 및 프로그램 매매 관련 불확실성 존재.</t>
+          <t>빅파마 기술이전 3상 4건 진행 중. 락업 해제 물량 소화 및 프로그램 매매 부재 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['3상', '기술이전', '락업해제']</t>
+          <t>['기술이전', '3상', '락업해제']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85600</v>
+        <v>85900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F18" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G18" t="n">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>76612929600</v>
+        <v>78869967000</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 언급. 120일선 돌파 기대감. 외인 매도세 속 개인 투자자 참여.</t>
+          <t>미국 증시 원전주 급등 및 대미 투자 관련 발표 가능성 뉴스를 기반으로 상승 기대감 형성. 다만, 구체적인 공시나 실적 발표보다는 소문과 기대에 기반한 분위기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '외인']</t>
+          <t>['원전주', '대미 투자', '뉴스']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10230</v>
+        <v>10210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.57%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>20817936300</v>
+        <v>21219983425</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4165</v>
+        <v>4185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-10.14%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F20" t="n">
         <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>31297100986</v>
+        <v>31633271996</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 코인 관련 호재 언급 속 하락세 지속. 공매도 압박 및 주가 하락 예상.</t>
+          <t>STO 사업 추진 및 미국 코인 관련 호재 언급. 주가 하락 가능성 및 경고 예고.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['STO', '코인', '공매도']</t>
+          <t>['STO', '코인', '호재']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_11.xlsx
+++ b/data/trending_integrated_20260918_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8370</v>
+        <v>25800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.23%</t>
+          <t>'+19.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7020</v>
+        <v>21600</v>
       </c>
       <c r="K2" t="n">
-        <v>7180</v>
+        <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>8890</v>
+        <v>25950</v>
       </c>
       <c r="M2" t="n">
-        <v>7150</v>
+        <v>21700</v>
       </c>
       <c r="N2" t="n">
-        <v>0.59</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>135793291690</v>
+        <v>245043860350</v>
       </c>
       <c r="P2" t="n">
-        <v>16200</v>
+        <v>59600</v>
       </c>
       <c r="Q2" t="n">
-        <v>1206</v>
+        <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>619000</v>
+        <v>-170000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>연말까지 홀딩하며 평정심 유지 강조. 일부 매물대 및 하락 우려 언급.</t>
+          <t>과거 고점 언급 및 재진입 기대. 외인, 프로그램 폭풍 매수. 박스권 상단 돌파.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['홀딩', '평정심', '매물대']</t>
+          <t>['외인', '프로그램', '박스권']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25400</v>
+        <v>8320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.59%</t>
+          <t>'+18.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="H3" t="n">
-        <v>2.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21600</v>
+        <v>7020</v>
       </c>
       <c r="K3" t="n">
-        <v>22250</v>
+        <v>7180</v>
       </c>
       <c r="L3" t="n">
-        <v>25950</v>
+        <v>8890</v>
       </c>
       <c r="M3" t="n">
-        <v>21700</v>
+        <v>7150</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>238484105325</v>
+        <v>137216255920</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>-170000</v>
+        <v>619000</v>
       </c>
       <c r="S3" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 폭풍 매수 확인. 박스권 상단 돌파 및 대장주 움직임 언급.</t>
+          <t>연말 홀딩 및 10000원 돌파 기대. 개미 매도, 외국인 매수 관찰. 매물대 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외인', '매수', '박스권']</t>
+          <t>['홀딩', '외국인', '매물대']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18500</v>
+        <v>18480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+14.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F4" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
-        <v>1556</v>
+        <v>1608</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>564870798060</v>
+        <v>576645629520</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>수익률 500% 이상 달성 언급. 숏커버링 발생 및 외인 기관 투신 매수세 확인.</t>
+          <t>수익률 520% 달성 언급. ETF 대란 및 공매도 관련 내용. 2차 매물대 돌파 및 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수익률', '숏커버링', '매수세']</t>
+          <t>['공매도', '숏커버링', '매물대']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31550</v>
+        <v>31600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.48%</t>
+          <t>'+11.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>164157481075</v>
+        <v>167183268875</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선 대비 저평가 해소 기대. 연기금 매수세 유입 확인.</t>
+          <t>가온전선과의 비교 및 저평가 해소 기대감. 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '연기금', '매수세']</t>
+          <t>['저평가', '연기금', '추세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12890</v>
+        <v>12850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+10.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
@@ -978,7 +978,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>111990884700</v>
+        <v>112857972220</v>
       </c>
       <c r="P6" t="n">
         <v>21150</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11710</v>
+        <v>11670</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.37%</t>
+          <t>'+9.99%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
         <v>12.5</v>
@@ -1070,7 +1070,7 @@
         <v>12.6</v>
       </c>
       <c r="O7" t="n">
-        <v>92917928560</v>
+        <v>93885099560</v>
       </c>
       <c r="P7" t="n">
         <v>14350</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6470</v>
+        <v>6450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.03%</t>
+          <t>'+9.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H8" t="n">
         <v>2.85</v>
@@ -1162,7 +1162,7 @@
         <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>81923254005</v>
+        <v>82490990430</v>
       </c>
       <c r="P8" t="n">
         <v>11760</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 저평가 상태 언급. 전환사채 발행 가능성 언급.</t>
+          <t>저평가 구간 언급 및 박스권 돌파. 외국인, 프로그램 매수세 유입. 변압기 관련주.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['박스권', '저평가', '전환사채']</t>
+          <t>['저평가', '박스권', '변압기']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13970</v>
+        <v>13990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.63%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H9" t="n">
         <v>2.83</v>
@@ -1254,7 +1254,7 @@
         <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>126536811975</v>
+        <v>127658229830</v>
       </c>
       <c r="P9" t="n">
         <v>20300</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13950</v>
+        <v>13940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.65%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1346,7 +1346,7 @@
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>50319726095</v>
+        <v>51676849090</v>
       </c>
       <c r="P10" t="n">
         <v>30200</v>
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G11" t="n">
-        <v>2592</v>
+        <v>2461</v>
       </c>
       <c r="H11" t="n">
         <v>50.1</v>
@@ -1438,7 +1438,7 @@
         <v>50.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2227295082500</v>
+        <v>2303674150000</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 반도체주 급등 영향. 반도체 펀더멘털 튼튼 및 수요 많음 언급.</t>
+          <t>연말 500 예상 및 추석 랠리 기대. 외인 순매수 전환 및 자사주 매입 시작. 반도체 수요 증가.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '수요', '펀더멘털']</t>
+          <t>['외인', '자사주매입', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19290</v>
+        <v>19200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.33%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H12" t="n">
         <v>10.74</v>
@@ -1530,7 +1530,7 @@
         <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>94378722850</v>
+        <v>95967396485</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 요구. 중동 전쟁 종전 논의 및 하반기 상승 기대.</t>
+          <t>미국장 및 중동 정세 관련 상승 기대감. 대차해지 운동 참여 독려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '중동 전쟁', '상승 기대']</t>
+          <t>['대차해지', '중동', '건설']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13780</v>
+        <v>52700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>232</v>
+        <v>362</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>38.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13360</v>
+        <v>51100</v>
       </c>
       <c r="K13" t="n">
-        <v>13450</v>
+        <v>51600</v>
       </c>
       <c r="L13" t="n">
-        <v>14450</v>
+        <v>55200</v>
       </c>
       <c r="M13" t="n">
-        <v>13450</v>
+        <v>51500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>32099337640</v>
+        <v>183619502450</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>499000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>123000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>['외인', '기관', '매수세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52600</v>
+        <v>259000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>450</v>
       </c>
       <c r="G14" t="n">
-        <v>358</v>
+        <v>1935</v>
       </c>
       <c r="H14" t="n">
-        <v>38.54</v>
+        <v>46.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51100</v>
+        <v>252500</v>
       </c>
       <c r="K14" t="n">
-        <v>51600</v>
+        <v>261000</v>
       </c>
       <c r="L14" t="n">
-        <v>55200</v>
+        <v>261000</v>
       </c>
       <c r="M14" t="n">
-        <v>51500</v>
+        <v>257500</v>
       </c>
       <c r="N14" t="n">
-        <v>38.62</v>
+        <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>180618295700</v>
+        <v>1315642594750</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>78600</v>
       </c>
       <c r="R14" t="n">
-        <v>499000</v>
+        <v>-601000</v>
       </c>
       <c r="S14" t="n">
-        <v>123000</v>
+        <v>333000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
+          <t>정치 관련 내용이 주를 이루며, 삼성전자 주가 상승에 대한 언급은 적음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인', '기관', '매수세']</t>
+          <t>['기자회견', '정치', '이재명']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>259000</v>
+        <v>13680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>454</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>1845</v>
+        <v>234</v>
       </c>
       <c r="H15" t="n">
-        <v>46.48</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>252500</v>
+        <v>13360</v>
       </c>
       <c r="K15" t="n">
-        <v>261000</v>
+        <v>13450</v>
       </c>
       <c r="L15" t="n">
-        <v>261000</v>
+        <v>14450</v>
       </c>
       <c r="M15" t="n">
-        <v>257500</v>
+        <v>13450</v>
       </c>
       <c r="N15" t="n">
-        <v>46.52</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1276087076500</v>
+        <v>32326192860</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>78600</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-601000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치 관련 내용 중심, 주가 상승 관련 내용은 적음.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17600</v>
+        <v>17550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H16" t="n">
         <v>0.97</v>
@@ -1898,7 +1898,7 @@
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>68652716070</v>
+        <v>69076578275</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18080</v>
+        <v>18070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.84%</t>
+          <t>'+0.78%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>70756277325</v>
+        <v>71469761210</v>
       </c>
       <c r="P17" t="n">
         <v>21100</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>빅파마 기술이전 3상 4건 진행 중. 락업 해제 물량 소화 및 프로그램 매매 부재 언급.</t>
+          <t>락업 해제 및 엑시트 물량 소화 중. 빅파마 3상 관련 내용 언급. 매도세 관찰.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['기술이전', '3상', '락업해제']</t>
+          <t>['락업해제', '엑시트', '3상']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G18" t="n">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>78869967000</v>
+        <v>79740146000</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10210</v>
+        <v>10200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>21219983425</v>
+        <v>21497543915</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4185</v>
+        <v>4195</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'-9.49%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F20" t="n">
         <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>31633271996</v>
+        <v>31847273466</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 관련 호재 언급. 주가 하락 가능성 및 경고 예고.</t>
+          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급. 일부 매도 의견 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>
